--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -4043,7 +4043,7 @@
         <v>135708112</v>
       </c>
       <c r="B32" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135708120</v>
       </c>
       <c r="B33" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135708141</v>
       </c>
       <c r="B34" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135708144</v>
       </c>
       <c r="B35" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135708145</v>
       </c>
       <c r="B36" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135708188</v>
       </c>
       <c r="B37" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135708191</v>
       </c>
       <c r="B38" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
